--- a/ig/DM-37/CodeSystem-terminologie-emdn.xlsx
+++ b/ig/DM-37/CodeSystem-terminologie-emdn.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-emdn</t>
+    <t>OID:1.2.250.1.213.2.68</t>
   </si>
   <si>
     <t>Version</t>
